--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486866_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486866_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>P. BONO SOLER</t>
+          <t>A. RIVAS PALMER</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,64 +565,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.0068</v>
+        <v>7.3002</v>
       </c>
       <c r="E2" t="n">
-        <v>3.245</v>
+        <v>6.6148</v>
       </c>
       <c r="F2" t="n">
-        <v>3.7618</v>
+        <v>0.6853</v>
       </c>
       <c r="G2" t="n">
-        <v>3.9773</v>
+        <v>4.4546</v>
       </c>
       <c r="H2" t="n">
-        <v>1.5408</v>
+        <v>0.2819</v>
       </c>
       <c r="I2" t="n">
-        <v>2.4365</v>
+        <v>4.1727</v>
       </c>
       <c r="J2" t="n">
-        <v>2.106</v>
+        <v>6.1376</v>
       </c>
       <c r="K2" t="n">
-        <v>0.6458</v>
+        <v>1.3626</v>
       </c>
       <c r="L2" t="n">
-        <v>1.4602</v>
+        <v>4.775</v>
       </c>
       <c r="M2" t="n">
-        <v>1.8713</v>
+        <v>-1.683</v>
       </c>
       <c r="N2" t="n">
-        <v>0.895</v>
+        <v>-1.0807</v>
       </c>
       <c r="O2" t="n">
-        <v>0.9762999999999999</v>
+        <v>-0.6022999999999999</v>
       </c>
       <c r="P2" t="n">
-        <v>1.0267</v>
+        <v>0.616</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>-1.0267</v>
       </c>
       <c r="R2" t="n">
-        <v>1.0267</v>
+        <v>1.6427</v>
       </c>
       <c r="S2" t="n">
-        <v>2.0028</v>
+        <v>1.0509</v>
       </c>
       <c r="T2" t="n">
-        <v>1.1389</v>
+        <v>0.3253</v>
       </c>
       <c r="U2" t="n">
-        <v>0.8638</v>
+        <v>0.7256</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.1786</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.1786</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. RIVAS PALMER</t>
+          <t>K. CLEMENT AIGBOGUN</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.2954</v>
+        <v>6.4486</v>
       </c>
       <c r="E3" t="n">
-        <v>5.5804</v>
+        <v>3.9262</v>
       </c>
       <c r="F3" t="n">
-        <v>0.715</v>
+        <v>2.5224</v>
       </c>
       <c r="G3" t="n">
-        <v>4.4546</v>
+        <v>6.4065</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2819</v>
+        <v>1.9917</v>
       </c>
       <c r="I3" t="n">
-        <v>4.1727</v>
+        <v>4.4148</v>
       </c>
       <c r="J3" t="n">
-        <v>6.1376</v>
+        <v>5.1192</v>
       </c>
       <c r="K3" t="n">
-        <v>1.3626</v>
+        <v>1.5412</v>
       </c>
       <c r="L3" t="n">
-        <v>4.775</v>
+        <v>3.578</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.683</v>
+        <v>1.2873</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.0807</v>
+        <v>0.4505</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.6022999999999999</v>
+        <v>0.8368</v>
       </c>
       <c r="P3" t="n">
-        <v>0.616</v>
+        <v>-1.0267</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.0267</v>
+        <v>-2.0534</v>
       </c>
       <c r="R3" t="n">
-        <v>1.6427</v>
+        <v>1.0267</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0461</v>
+        <v>0.4795</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.7091</v>
+        <v>0.2711</v>
       </c>
       <c r="U3" t="n">
-        <v>0.7552</v>
+        <v>0.2084</v>
       </c>
       <c r="V3" t="n">
-        <v>1.1786</v>
+        <v>0.5893</v>
       </c>
       <c r="W3" t="n">
-        <v>1.1786</v>
+        <v>0.5893</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>D. KANDULU</t>
+          <t>J. PALAMOS MOLINS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>6.2114</v>
+        <v>6.1581</v>
       </c>
       <c r="E4" t="n">
-        <v>1.8739</v>
+        <v>3.7522</v>
       </c>
       <c r="F4" t="n">
-        <v>4.3375</v>
+        <v>2.4059</v>
       </c>
       <c r="G4" t="n">
-        <v>4.5713</v>
+        <v>5.2939</v>
       </c>
       <c r="H4" t="n">
-        <v>3.4133</v>
+        <v>0.1684</v>
       </c>
       <c r="I4" t="n">
-        <v>1.1579</v>
+        <v>5.1256</v>
       </c>
       <c r="J4" t="n">
-        <v>3.9391</v>
+        <v>3.8143</v>
       </c>
       <c r="K4" t="n">
-        <v>2.9919</v>
+        <v>-0.1718</v>
       </c>
       <c r="L4" t="n">
-        <v>0.9472</v>
+        <v>3.986</v>
       </c>
       <c r="M4" t="n">
-        <v>0.6321</v>
+        <v>1.4796</v>
       </c>
       <c r="N4" t="n">
-        <v>0.4214</v>
+        <v>0.3401</v>
       </c>
       <c r="O4" t="n">
-        <v>0.2107</v>
+        <v>1.1395</v>
       </c>
       <c r="P4" t="n">
-        <v>-1.4374</v>
+        <v>1.8481</v>
       </c>
       <c r="Q4" t="n">
-        <v>-3.0801</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.6427</v>
+        <v>1.8481</v>
       </c>
       <c r="S4" t="n">
-        <v>2.3794</v>
+        <v>0.435</v>
       </c>
       <c r="T4" t="n">
-        <v>1.0149</v>
+        <v>-0.0621</v>
       </c>
       <c r="U4" t="n">
-        <v>1.3644</v>
+        <v>0.4971</v>
       </c>
       <c r="V4" t="n">
-        <v>0.6982</v>
+        <v>-1.4189</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0.6982</v>
+        <v>-1.4189</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>K. CLEMENT AIGBOGUN</t>
+          <t>P. BONO SOLER</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>6.1547</v>
+        <v>6.0144</v>
       </c>
       <c r="E5" t="n">
-        <v>3.8991</v>
+        <v>2.5786</v>
       </c>
       <c r="F5" t="n">
-        <v>2.2556</v>
+        <v>3.4358</v>
       </c>
       <c r="G5" t="n">
-        <v>6.4065</v>
+        <v>3.9773</v>
       </c>
       <c r="H5" t="n">
-        <v>1.9917</v>
+        <v>1.5408</v>
       </c>
       <c r="I5" t="n">
-        <v>4.4148</v>
+        <v>2.4365</v>
       </c>
       <c r="J5" t="n">
-        <v>5.1192</v>
+        <v>2.106</v>
       </c>
       <c r="K5" t="n">
-        <v>1.5412</v>
+        <v>0.6458</v>
       </c>
       <c r="L5" t="n">
-        <v>3.578</v>
+        <v>1.4602</v>
       </c>
       <c r="M5" t="n">
-        <v>1.2873</v>
+        <v>1.8713</v>
       </c>
       <c r="N5" t="n">
-        <v>0.4505</v>
+        <v>0.895</v>
       </c>
       <c r="O5" t="n">
-        <v>0.8368</v>
+        <v>0.9762999999999999</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.0267</v>
+        <v>1.0267</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.0534</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
         <v>1.0267</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1856</v>
+        <v>1.0103</v>
       </c>
       <c r="T5" t="n">
-        <v>0.244</v>
+        <v>0.4726</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0584</v>
+        <v>0.5377</v>
       </c>
       <c r="V5" t="n">
-        <v>0.5893</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0.5893</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. PALAMOS MOLINS</t>
+          <t>D. KANDULU</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>5.1114</v>
+        <v>5.3228</v>
       </c>
       <c r="E6" t="n">
-        <v>3.0315</v>
+        <v>1.5485</v>
       </c>
       <c r="F6" t="n">
-        <v>2.0799</v>
+        <v>3.7743</v>
       </c>
       <c r="G6" t="n">
-        <v>5.2939</v>
+        <v>4.5713</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1684</v>
+        <v>3.4133</v>
       </c>
       <c r="I6" t="n">
-        <v>5.1256</v>
+        <v>1.1579</v>
       </c>
       <c r="J6" t="n">
-        <v>3.8143</v>
+        <v>3.9391</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.1718</v>
+        <v>2.9919</v>
       </c>
       <c r="L6" t="n">
-        <v>3.986</v>
+        <v>0.9472</v>
       </c>
       <c r="M6" t="n">
-        <v>1.4796</v>
+        <v>0.6321</v>
       </c>
       <c r="N6" t="n">
-        <v>0.3401</v>
+        <v>0.4214</v>
       </c>
       <c r="O6" t="n">
-        <v>1.1395</v>
+        <v>0.2107</v>
       </c>
       <c r="P6" t="n">
-        <v>1.8481</v>
+        <v>-1.4374</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-3.0801</v>
       </c>
       <c r="R6" t="n">
-        <v>1.8481</v>
+        <v>1.6427</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.6117</v>
+        <v>1.4908</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.7827</v>
+        <v>0.6895</v>
       </c>
       <c r="U6" t="n">
-        <v>0.171</v>
+        <v>0.8012</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.4189</v>
+        <v>0.6982</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.4189</v>
+        <v>0.6982</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>4.6722</v>
+        <v>4.2792</v>
       </c>
       <c r="E7" t="n">
-        <v>3.9528</v>
+        <v>3.3523</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7194</v>
+        <v>0.9268999999999999</v>
       </c>
       <c r="G7" t="n">
         <v>0.7445000000000001</v>
@@ -1000,13 +1000,13 @@
         <v>1.6427</v>
       </c>
       <c r="S7" t="n">
-        <v>1.6957</v>
+        <v>1.3027</v>
       </c>
       <c r="T7" t="n">
-        <v>1.5805</v>
+        <v>0.9801</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1152</v>
+        <v>0.3226</v>
       </c>
       <c r="V7" t="n">
         <v>0.5893</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>3.1146</v>
+        <v>2.5769</v>
       </c>
       <c r="E8" t="n">
-        <v>1.185</v>
+        <v>1.0029</v>
       </c>
       <c r="F8" t="n">
-        <v>1.9296</v>
+        <v>1.5739</v>
       </c>
       <c r="G8" t="n">
         <v>2.201</v>
@@ -1078,13 +1078,13 @@
         <v>1.2321</v>
       </c>
       <c r="S8" t="n">
-        <v>1.735</v>
+        <v>1.1972</v>
       </c>
       <c r="T8" t="n">
-        <v>0.6778</v>
+        <v>0.4958</v>
       </c>
       <c r="U8" t="n">
-        <v>1.0571</v>
+        <v>0.7014</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.6602</v>
+        <v>2.0085</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9360000000000001</v>
+        <v>1.1065</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7242</v>
+        <v>0.902</v>
       </c>
       <c r="G9" t="n">
         <v>1.7633</v>
@@ -1156,13 +1156,13 @@
         <v>1.4374</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1186</v>
+        <v>0.4669</v>
       </c>
       <c r="T9" t="n">
-        <v>0.2362</v>
+        <v>0.4067</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1177</v>
+        <v>0.0602</v>
       </c>
       <c r="V9" t="n">
         <v>-1.6591</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6846</v>
+        <v>1.3442</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0623</v>
+        <v>0.5737</v>
       </c>
       <c r="F10" t="n">
-        <v>0.6223</v>
+        <v>0.7705</v>
       </c>
       <c r="G10" t="n">
         <v>3.454</v>
@@ -1234,13 +1234,13 @@
         <v>1.2321</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1801</v>
+        <v>0.4795</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5851</v>
+        <v>-0.0737</v>
       </c>
       <c r="U10" t="n">
-        <v>0.405</v>
+        <v>0.5532</v>
       </c>
       <c r="V10" t="n">
         <v>-1.7679</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.2382</v>
+        <v>0.3399</v>
       </c>
       <c r="E11" t="n">
-        <v>0.2374</v>
+        <v>0.5783</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.4756</v>
+        <v>-0.2384</v>
       </c>
       <c r="G11" t="n">
         <v>-0.5667</v>
@@ -1312,13 +1312,13 @@
         <v>1.0267</v>
       </c>
       <c r="S11" t="n">
-        <v>0.3285</v>
+        <v>0.9066</v>
       </c>
       <c r="T11" t="n">
-        <v>0.3834</v>
+        <v>0.7244</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.055</v>
+        <v>0.1822</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.71</v>
+        <v>-2.383</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.5745</v>
+        <v>-2.129</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.1354</v>
+        <v>-0.254</v>
       </c>
       <c r="G12" t="n">
         <v>-3.7584</v>
@@ -1390,13 +1390,13 @@
         <v>0.4107</v>
       </c>
       <c r="S12" t="n">
-        <v>0.3975</v>
+        <v>0.7245</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.1822</v>
+        <v>0.2634</v>
       </c>
       <c r="U12" t="n">
-        <v>0.5797</v>
+        <v>0.4611</v>
       </c>
       <c r="V12" t="n">
         <v>0.2402</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.2392</v>
+        <v>-3.039</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.1849</v>
+        <v>-2.0144</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.0543</v>
+        <v>-1.0246</v>
       </c>
       <c r="G13" t="n">
         <v>-2.3635</v>
@@ -1468,13 +1468,13 @@
         <v>0.2053</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.2515</v>
+        <v>-0.0513</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.1317</v>
+        <v>0.0387</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.1197</v>
+        <v>-0.0901</v>
       </c>
       <c r="V13" t="n">
         <v>-0.8295</v>
@@ -1501,10 +1501,10 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>34.7239</v>
+        <v>36.3708</v>
       </c>
       <c r="E14" t="n">
-        <v>19.244</v>
+        <v>20.8906</v>
       </c>
       <c r="F14" t="n">
         <v>15.48</v>
@@ -1513,7 +1513,7 @@
         <v>26.1778</v>
       </c>
       <c r="H14" t="n">
-        <v>8.774700000000003</v>
+        <v>8.774700000000001</v>
       </c>
       <c r="I14" t="n">
         <v>17.4034</v>
@@ -1522,7 +1522,7 @@
         <v>24.815</v>
       </c>
       <c r="K14" t="n">
-        <v>9.978799999999998</v>
+        <v>9.9788</v>
       </c>
       <c r="L14" t="n">
         <v>14.8361</v>
@@ -1534,10 +1534,10 @@
         <v>-1.2043</v>
       </c>
       <c r="O14" t="n">
-        <v>2.567</v>
+        <v>2.567000000000001</v>
       </c>
       <c r="P14" t="n">
-        <v>3.079999999999999</v>
+        <v>3.08</v>
       </c>
       <c r="Q14" t="n">
         <v>-11.2937</v>
@@ -1546,10 +1546,10 @@
         <v>14.3739</v>
       </c>
       <c r="S14" t="n">
-        <v>7.8459</v>
+        <v>9.492599999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>2.8849</v>
+        <v>4.5318</v>
       </c>
       <c r="U14" t="n">
         <v>4.9606</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.4731</v>
+        <v>1.5027</v>
       </c>
       <c r="E15" t="n">
         <v>0.9031</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5699</v>
+        <v>0.5996</v>
       </c>
       <c r="G15" t="n">
         <v>0.4184</v>
@@ -1624,13 +1624,13 @@
         <v>0.2053</v>
       </c>
       <c r="S15" t="n">
-        <v>0.0198</v>
+        <v>0.0494</v>
       </c>
       <c r="T15" t="n">
         <v>0.0736</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0538</v>
+        <v>-0.0242</v>
       </c>
       <c r="V15" t="n">
         <v>0.8295</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.4727</v>
+        <v>0.837</v>
       </c>
       <c r="E16" t="n">
-        <v>1.498</v>
+        <v>1.8118</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.0253</v>
+        <v>-0.9748</v>
       </c>
       <c r="G16" t="n">
         <v>1.0851</v>
@@ -1702,13 +1702,13 @@
         <v>1.0267</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.3804</v>
+        <v>-1.016</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.1857</v>
+        <v>-0.8719</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1947</v>
+        <v>-0.1442</v>
       </c>
       <c r="V16" t="n">
         <v>1.1786</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.3832</v>
+        <v>-0.3536</v>
       </c>
       <c r="E17" t="n">
         <v>-0.9530999999999999</v>
       </c>
       <c r="F17" t="n">
-        <v>0.5699</v>
+        <v>0.5996</v>
       </c>
       <c r="G17" t="n">
         <v>0.4184</v>
@@ -1780,13 +1780,13 @@
         <v>0.2053</v>
       </c>
       <c r="S17" t="n">
-        <v>0.0198</v>
+        <v>0.0494</v>
       </c>
       <c r="T17" t="n">
         <v>0.0736</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0538</v>
+        <v>-0.0242</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.468</v>
+        <v>-0.659</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.0412</v>
+        <v>0.2727</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.4269</v>
+        <v>-0.9317</v>
       </c>
       <c r="G18" t="n">
         <v>-0.8268</v>
@@ -1858,13 +1858,13 @@
         <v>0.8214</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.7931</v>
+        <v>-0.9841</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.1857</v>
+        <v>-0.8719</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.6074000000000001</v>
+        <v>-0.1122</v>
       </c>
       <c r="V18" t="n">
         <v>1.7679</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>P. RENANE</t>
+          <t>P. SALA VALLMAJO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.8497</v>
+        <v>-1.7815</v>
       </c>
       <c r="E19" t="n">
-        <v>0.2901</v>
+        <v>-0.4432</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.1397</v>
+        <v>-1.3384</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.2351</v>
+        <v>-1.6194</v>
       </c>
       <c r="H19" t="n">
-        <v>-2.2773</v>
+        <v>0.6486</v>
       </c>
       <c r="I19" t="n">
-        <v>0.0421</v>
+        <v>-2.2679</v>
       </c>
       <c r="J19" t="n">
-        <v>1.3131</v>
+        <v>0.3319</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.002</v>
+        <v>1.6741</v>
       </c>
       <c r="L19" t="n">
-        <v>2.3151</v>
+        <v>-1.3422</v>
       </c>
       <c r="M19" t="n">
-        <v>-3.5483</v>
+        <v>-1.9512</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.2753</v>
+        <v>-1.0255</v>
       </c>
       <c r="O19" t="n">
-        <v>-2.2729</v>
+        <v>-0.9257</v>
       </c>
       <c r="P19" t="n">
-        <v>0.2053</v>
+        <v>1.2321</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.2321</v>
+        <v>-0.2053</v>
       </c>
       <c r="R19" t="n">
         <v>1.4374</v>
       </c>
       <c r="S19" t="n">
-        <v>0.1801</v>
+        <v>-0.8048999999999999</v>
       </c>
       <c r="T19" t="n">
-        <v>0.209</v>
+        <v>-0.5697</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0289</v>
+        <v>-0.2352</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>-0.5893</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-0.5893</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>P. SALA VALLMAJO</t>
+          <t>P. RENANE</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.8049</v>
+        <v>-2.3466</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.8616</v>
+        <v>-0.3376</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.9434</v>
+        <v>-2.009</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.6194</v>
+        <v>-2.2351</v>
       </c>
       <c r="H20" t="n">
-        <v>0.6486</v>
+        <v>-2.2773</v>
       </c>
       <c r="I20" t="n">
-        <v>-2.2679</v>
+        <v>0.0421</v>
       </c>
       <c r="J20" t="n">
-        <v>0.3319</v>
+        <v>1.3131</v>
       </c>
       <c r="K20" t="n">
-        <v>1.6741</v>
+        <v>-1.002</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.3422</v>
+        <v>2.3151</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.9512</v>
+        <v>-3.5483</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.0255</v>
+        <v>-1.2753</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.9257</v>
+        <v>-2.2729</v>
       </c>
       <c r="P20" t="n">
-        <v>1.2321</v>
+        <v>0.2053</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.2053</v>
+        <v>-1.2321</v>
       </c>
       <c r="R20" t="n">
         <v>1.4374</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.8283</v>
+        <v>-0.3168</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.9881</v>
+        <v>-0.4186</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.8401999999999999</v>
+        <v>0.1019</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.5893</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.5893</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.8212</v>
+        <v>-2.8439</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.2985</v>
+        <v>-1.1939</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.5227</v>
+        <v>-1.65</v>
       </c>
       <c r="G21" t="n">
         <v>-2.0967</v>
@@ -2092,13 +2092,13 @@
         <v>0.4107</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.5458</v>
+        <v>-0.5686</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5851</v>
+        <v>-0.4805</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0393</v>
+        <v>-0.08799999999999999</v>
       </c>
       <c r="V21" t="n">
         <v>-0.5893</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>S. KANE</t>
+          <t>X. TORRENT BAYÉ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.4098</v>
+        <v>-3.101</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.3093</v>
+        <v>-1.6021</v>
       </c>
       <c r="F22" t="n">
-        <v>0.8995</v>
+        <v>-1.499</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.9639</v>
+        <v>-3.2754</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.9616</v>
+        <v>-0.9863</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.0023</v>
+        <v>-2.289</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.8334</v>
+        <v>-1.2184</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.9913</v>
+        <v>-0.6</v>
       </c>
       <c r="L22" t="n">
-        <v>0.1579</v>
+        <v>-0.6183999999999999</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.1305</v>
+        <v>-2.0569</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.9703000000000001</v>
+        <v>-0.3863</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.1602</v>
+        <v>-1.6706</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.6427</v>
+        <v>1.0267</v>
       </c>
       <c r="Q22" t="n">
-        <v>-3.2855</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.6427</v>
+        <v>1.0267</v>
       </c>
       <c r="S22" t="n">
-        <v>1.1968</v>
+        <v>-0.6122</v>
       </c>
       <c r="T22" t="n">
-        <v>0.8096</v>
+        <v>-0.3836</v>
       </c>
       <c r="U22" t="n">
-        <v>0.3873</v>
+        <v>-0.2285</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>-0.2402</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-0.2402</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X. TORRENT BAYÉ</t>
+          <t>S. KANE</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.7078</v>
+        <v>-4.0845</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.8113</v>
+        <v>-4.937</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.8965</v>
+        <v>0.8524</v>
       </c>
       <c r="G23" t="n">
-        <v>-3.2754</v>
+        <v>-2.9639</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.9863</v>
+        <v>-2.9616</v>
       </c>
       <c r="I23" t="n">
-        <v>-2.289</v>
+        <v>-0.0023</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.2184</v>
+        <v>-1.8334</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.6</v>
+        <v>-1.9913</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.6183999999999999</v>
+        <v>0.1579</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.0569</v>
+        <v>-1.1305</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.3863</v>
+        <v>-0.9703000000000001</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.6706</v>
+        <v>-0.1602</v>
       </c>
       <c r="P23" t="n">
-        <v>1.0267</v>
+        <v>-1.6427</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>-3.2855</v>
       </c>
       <c r="R23" t="n">
-        <v>1.0267</v>
+        <v>1.6427</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.2189</v>
+        <v>0.5221</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.5928</v>
+        <v>0.182</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.626</v>
+        <v>0.3401</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.2402</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.2402</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.6683</v>
+        <v>-4.8391</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.0338</v>
+        <v>-2.6614</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.6345</v>
+        <v>-2.1777</v>
       </c>
       <c r="G24" t="n">
         <v>-3.3037</v>
@@ -2326,13 +2326,13 @@
         <v>1.2321</v>
       </c>
       <c r="S24" t="n">
-        <v>0.09130000000000001</v>
+        <v>-0.0795</v>
       </c>
       <c r="T24" t="n">
-        <v>0.612</v>
+        <v>-0.0156</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.5206</v>
+        <v>-0.0638</v>
       </c>
       <c r="V24" t="n">
         <v>1.4189</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-7.3446</v>
+        <v>-6.6228</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.65</v>
+        <v>-2.127</v>
       </c>
       <c r="F25" t="n">
-        <v>-4.6946</v>
+        <v>-4.4958</v>
       </c>
       <c r="G25" t="n">
         <v>-4.5162</v>
@@ -2404,13 +2404,13 @@
         <v>0.8214</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.7195</v>
+        <v>-0.9977</v>
       </c>
       <c r="T25" t="n">
-        <v>-1.3174</v>
+        <v>-0.7944</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.4021</v>
+        <v>-0.2033</v>
       </c>
       <c r="V25" t="n">
         <v>-0.6982</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-8.212199999999999</v>
+        <v>-8.339499999999999</v>
       </c>
       <c r="E26" t="n">
         <v>-4.2124</v>
       </c>
       <c r="F26" t="n">
-        <v>-3.9998</v>
+        <v>-4.1271</v>
       </c>
       <c r="G26" t="n">
         <v>-7.2626</v>
@@ -2482,13 +2482,13 @@
         <v>1.0267</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.8675</v>
+        <v>-0.9948</v>
       </c>
       <c r="T26" t="n">
         <v>-0.8836000000000001</v>
       </c>
       <c r="U26" t="n">
-        <v>0.0161</v>
+        <v>-0.1112</v>
       </c>
       <c r="V26" t="n">
         <v>-0.6982</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-34.7239</v>
+        <v>-32.6318</v>
       </c>
       <c r="E27" t="n">
-        <v>-15.48</v>
+        <v>-15.4801</v>
       </c>
       <c r="F27" t="n">
-        <v>-19.2441</v>
+        <v>-17.1519</v>
       </c>
       <c r="G27" t="n">
         <v>-26.1779</v>
@@ -2545,7 +2545,7 @@
         <v>-24.8151</v>
       </c>
       <c r="N27" t="n">
-        <v>-9.978900000000001</v>
+        <v>-9.978899999999999</v>
       </c>
       <c r="O27" t="n">
         <v>-14.8362</v>
@@ -2560,13 +2560,13 @@
         <v>11.2938</v>
       </c>
       <c r="S27" t="n">
-        <v>-7.845699999999999</v>
+        <v>-5.7537</v>
       </c>
       <c r="T27" t="n">
-        <v>-4.960599999999999</v>
+        <v>-4.9606</v>
       </c>
       <c r="U27" t="n">
-        <v>-2.8848</v>
+        <v>-0.7927999999999999</v>
       </c>
       <c r="V27" t="n">
         <v>2.379700000000001</v>
